--- a/2026/ЗАВОДЫ/Останкино/ОПТы/01,26/21,01,26 Ост КИ ПРС ЛП/ПРС ЛП 25,01.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/ОПТы/01,26/21,01,26 Ост КИ ПРС ЛП/ПРС ЛП 25,01.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV_Poliakov_PRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCB263F-9DB8-40AC-8C24-53C89B7BF210}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F365DEB2-639A-475C-93CC-96C2C8ADE5F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -353,7 +353,7 @@
         <v>1001225406754</v>
       </c>
       <c r="B1">
-        <v>286</v>
+        <v>572</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -361,7 +361,7 @@
         <v>1001303637233</v>
       </c>
       <c r="B2">
-        <v>210</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -369,7 +369,7 @@
         <v>1001223297103</v>
       </c>
       <c r="B3">
-        <v>459</v>
+        <v>918</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -377,7 +377,7 @@
         <v>1001094053215</v>
       </c>
       <c r="B4">
-        <v>144</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -385,7 +385,7 @@
         <v>1001025767284</v>
       </c>
       <c r="B5">
-        <v>253</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -393,7 +393,7 @@
         <v>1001010106325</v>
       </c>
       <c r="B6">
-        <v>398</v>
+        <v>796</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -401,7 +401,7 @@
         <v>1001220226208</v>
       </c>
       <c r="B7">
-        <v>209</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -409,7 +409,7 @@
         <v>1001205386222</v>
       </c>
       <c r="B8">
-        <v>289</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -417,7 +417,7 @@
         <v>1001022657074</v>
       </c>
       <c r="B9">
-        <v>363</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -425,7 +425,7 @@
         <v>1001012486333</v>
       </c>
       <c r="B10">
-        <v>257</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -433,7 +433,7 @@
         <v>1001012637334</v>
       </c>
       <c r="B11">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -441,7 +441,7 @@
         <v>1001225416228</v>
       </c>
       <c r="B12">
-        <v>373</v>
+        <v>673</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -449,7 +449,7 @@
         <v>1001205376221</v>
       </c>
       <c r="B13">
-        <v>211</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -457,7 +457,7 @@
         <v>1001060755931</v>
       </c>
       <c r="B14">
-        <v>344</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -465,7 +465,7 @@
         <v>1001203146834</v>
       </c>
       <c r="B15">
-        <v>133</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -473,7 +473,7 @@
         <v>1001025176475</v>
       </c>
       <c r="B16">
-        <v>268</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -481,7 +481,7 @@
         <v>1001203117382</v>
       </c>
       <c r="B17">
-        <v>366</v>
+        <v>650</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -489,7 +489,7 @@
         <v>1001303107241</v>
       </c>
       <c r="B18">
-        <v>250</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -497,7 +497,7 @@
         <v>1001063106937</v>
       </c>
       <c r="B19">
-        <v>166</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -505,7 +505,7 @@
         <v>1001300387154</v>
       </c>
       <c r="B20">
-        <v>252</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -513,7 +513,7 @@
         <v>1001022467080</v>
       </c>
       <c r="B21">
-        <v>310</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -521,7 +521,7 @@
         <v>1001022377066</v>
       </c>
       <c r="B22">
-        <v>358</v>
+        <v>700</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -529,7 +529,7 @@
         <v>1001022246713</v>
       </c>
       <c r="B23">
-        <v>357</v>
+        <v>650</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -537,7 +537,7 @@
         <v>1001012566392</v>
       </c>
       <c r="B24">
-        <v>503</v>
+        <v>800</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -545,7 +545,7 @@
         <v>1001302347177</v>
       </c>
       <c r="B25">
-        <v>212</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>1001012506353</v>
       </c>
       <c r="B26">
-        <v>233</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -561,7 +561,7 @@
         <v>1001062505483</v>
       </c>
       <c r="B27">
-        <v>187</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
